--- a/2018/Bekaa3/Bekaa3_members_final.xlsx
+++ b/2018/Bekaa3/Bekaa3_members_final.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
